--- a/Luban/Config/Datas/Levels/L26/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L26/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L26 W1/25; N=56; EHP=369.600000; normal:17x28,normal:18x28</t>
+          <t>L26 W1/25; N=56; EHP=1010.743271; normal:17x28,normal:18x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L26 W2/25; N=62; EHP=428.473320; normal:17x31,normal:18x31</t>
+          <t>L26 W2/25; N=62; EHP=1171.743844; normal:17x31,normal:18x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10020412,10020414,10048975,10020412,10020414,10048975,10020412,10020414,10048976,10020412,10020414,10048977,10020412,10020414,10048977,10020412,10020414,10048978,10020412,10020414,10048978,10020412,10020414,10048979,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020412,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413</t>
+          <t>10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020414,10020412,10020412,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020413,10020412,10020412,10020412,10020412,10020412,10020412,10020412,10020412</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L26 W3/25; N=68; EHP=520.000000; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x21,normal:18x20,swarm:84x19</t>
+          <t>L26 W3/25; N=68; EHP=1531.909390; normal:17x29,normal:18x20,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10020415,10020417,10048980,10020415,10020417,10048980,10020415,10020417,10048981,10020415,10020417,10048981,10020415,10020417,10048982,10020415,10020417,10048983,10020415,10020417,10048983,10020415,10020417,10048984,10020415,10020417,10048984,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020415,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416</t>
+          <t>10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020417,10020415,10020415,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416,10020416</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L26 W4/25; N=74; EHP=652.000000; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x22,normal:18x23,swarm:84x20</t>
+          <t>L26 W4/25; N=74; EHP=1925.260535; normal:17x22,normal:18x32,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10020418,10020421,10048985,10020420,10020418,10020421,10048985,10020420,10020418,10020421,10048986,10020420,10020418,10020421,10048986,10020420,10020418,10020421,10048987,10020422,10020418,10020421,10048987,10020422,10020418,10020421,10048988,10020422,10020418,10020421,10048988,10020422,10020418,10020421,10048989,10020423,10020418,10020421,10048989,10020423,10020418,10020421,10020423,10020418,10020421,10020423,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020419,10020421,10020419,10020421,10020419,10020421,10020419,10020421,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419</t>
+          <t>10020418,10048985,10048985,10020420,10020418,10048985,10048985,10020420,10020418,10048986,10048986,10020420,10020418,10048986,10048986,10020420,10020418,10048987,10048987,10020422,10020418,10048987,10048987,10020422,10020418,10048988,10048988,10020422,10020418,10048988,10048988,10020422,10020418,10048989,10048989,10020423,10020418,10048989,10048989,10020423,10020418,10020421,10020423,10020418,10020421,10020423,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020418,10020421,10020419,10020421,10020419,10020421,10020419,10020421,10020419,10020421,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419,10020419</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L26 W5/25; N=80; EHP=1216.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x18,medium:83x4,swarm:84x22,medium:108x4,medium:123x4</t>
+          <t>L26 W5/25; N=80; EHP=3369.609715; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x4,normal:17x18,normal:18x18,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10020427,10020433,10020429,10048990,10020432,10020427,10020433,10020429,10048990,10020432,10020427,10020433,10020429,10020424,10020432,10020427,10020433,10020430,10020424,10020432,10020427,10020433,10020430,10048991,10020435,10020427,10020433,10020431,10048991,10020435,10020427,10020433,10020431,10020425,10020435,10020427,10020433,10020434,10020425,10020435,10020427,10020433,10020434,10020426,10020436,10020427,10020433,10020434,10020426,10020436,10020427,10020433,10020436,10020427,10020433,10020436,10020427,10020433,10020427,10020433,10020427,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020428,10020428,10020428,10020428,10020428</t>
+          <t>10020427,10048990,10020429,10048990,10020432,10020427,10048990,10020429,10048990,10020432,10020427,10020424,10020429,10020424,10020432,10020427,10020424,10020430,10020424,10020432,10020427,10048991,10020430,10048991,10020435,10020427,10048991,10020431,10048991,10020435,10020427,10020425,10020431,10020425,10020435,10020427,10020425,10020434,10020425,10020435,10020427,10020426,10020434,10020426,10020436,10020427,10020426,10020434,10020426,10020436,10020427,10020433,10020436,10020427,10020433,10020436,10020427,10020433,10020427,10020433,10020427,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020433,10020428,10020428,10020428,10020428,10020428,10020428</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L26 W6/25; N=86; EHP=1241.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x24,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L26 W6/25; N=86; EHP=3436.715433; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10020440,10020446,10020442,10048992,10020445,10020440,10020446,10020442,10048992,10020445,10020440,10020446,10020443,10020437,10020445,10020440,10020446,10020443,10020437,10020445,10020440,10020446,10020443,10048993,10020445,10020440,10020446,10020444,10048993,10020448,10020440,10020446,10020444,10020438,10020448,10020440,10020446,10020444,10020438,10020448,10020440,10020446,10020447,10020439,10020448,10020440,10020446,10020447,10020439,10020449,10020440,10020446,10020447,10020439,10020449,10020440,10020446,10020449,10020440,10020446,10020449,10020440,10020446,10020440,10020446,10020440,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020441,10020441,10020441,10020441,10020441,10020441</t>
+          <t>10020440,10048992,10020442,10048992,10020445,10020440,10048992,10020442,10048992,10020445,10020440,10020437,10020443,10020437,10020445,10020440,10020437,10020443,10020437,10020445,10020440,10048993,10020443,10048993,10020445,10020440,10048993,10020444,10048993,10020448,10020440,10020438,10020444,10020438,10020448,10020440,10020438,10020444,10020438,10020448,10020440,10020439,10020447,10020439,10020448,10020440,10020439,10020447,10020439,10020449,10020440,10020439,10020447,10020439,10020449,10020440,10020446,10020449,10020440,10020446,10020449,10020440,10020446,10020440,10020446,10020440,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020446,10020441,10020441,10020441,10020441,10020441,10020441,10020441</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L26 W7/25; N=92; EHP=1392.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x5,swarm:84x25,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L26 W7/25; N=92; EHP=3856.162239; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10020453,10020459,10020455,10048994,10020458,10020453,10020459,10020455,10048994,10020458,10020453,10020459,10020455,10048994,10020458,10020453,10020459,10020456,10020450,10020458,10020453,10020459,10020456,10020450,10020461,10020453,10020459,10020456,10048995,10020461,10020453,10020459,10020457,10048995,10020461,10020453,10020459,10020457,10048995,10020461,10020453,10020459,10020457,10020451,10020461,10020453,10020459,10020460,10020451,10020462,10020453,10020459,10020460,10020452,10020462,10020453,10020459,10020452,10020462,10020453,10020459,10020462,10020453,10020459,10020462,10020453,10020459,10020453,10020459,10020453,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020454,10020454,10020454,10020454,10020454,10020454</t>
+          <t>10020453,10048994,10020455,10048994,10020458,10020453,10048994,10020455,10048994,10020458,10020453,10048994,10020455,10048994,10020458,10020453,10020450,10020456,10020450,10020458,10020453,10020450,10020456,10020450,10020461,10020453,10048995,10020456,10048995,10020461,10020453,10048995,10020457,10048995,10020461,10020453,10048995,10020457,10048995,10020461,10020453,10020451,10020457,10020451,10020461,10020453,10020451,10020460,10020451,10020462,10020453,10020452,10020460,10020452,10020462,10020453,10020452,10020452,10020462,10020453,10020459,10020462,10020453,10020459,10020462,10020453,10020459,10020453,10020459,10020453,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020459,10020454,10020454,10020454,10020454,10020454,10020454,10020454</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L26 W8/25; N=98; EHP=1788.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x17,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x4,swarm:84x27,fast:98x2,medium:108x5,medium:123x5</t>
+          <t>L26 W8/25; N=98; EHP=4954.757423; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x5,medium:123x5,normal:17x17,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10020466,10020472,10020468,10048996,10020471,10020466,10020472,10020468,10048996,10020471,10020466,10020472,10020468,10048996,10020471,10020466,10020472,10020469,10020463,10020471,10020466,10020472,10020469,10020463,10020471,10020466,10020472,10020469,10048997,10020474,10020466,10020472,10020470,10048997,10020474,10020466,10020472,10020470,10020464,10020474,10020466,10020472,10020470,10020464,10020474,10020466,10020472,10020473,10020464,10020474,10020466,10020472,10020473,10020465,10020475,10020466,10020472,10020473,10020465,10020475,10020466,10020472,10020475,10020466,10020472,10020475,10020466,10020472,10020475,10020466,10020472,10020466,10020472,10020466,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020467,10020467,10020467,10020467,10020467,10020467</t>
+          <t>10020466,10048996,10020468,10048996,10020471,10020466,10048996,10020468,10048996,10020471,10020466,10048996,10020468,10048996,10020471,10020466,10020463,10020469,10020463,10020471,10020466,10020463,10020469,10020463,10020471,10020466,10048997,10020469,10048997,10020474,10020466,10048997,10020470,10048997,10020474,10020466,10020464,10020470,10020464,10020474,10020466,10020464,10020470,10020464,10020474,10020466,10020464,10020473,10020464,10020474,10020466,10020465,10020473,10020465,10020475,10020466,10020465,10020473,10020465,10020475,10020466,10020472,10020475,10020466,10020472,10020475,10020466,10020472,10020475,10020466,10020472,10020466,10020472,10020466,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020472,10020467,10020467,10020467,10020467,10020467,10020467,10020467</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L26 W9/25; N=104; EHP=2280.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L26 W9/25; N=104; EHP=6313.084013; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10020479,10020485,10020481,10048998,10020484,10020479,10020485,10020481,10048998,10020484,10020479,10020485,10020481,10020476,10020484,10020479,10020485,10020481,10020476,10020484,10020479,10020485,10020482,10020476,10020484,10020479,10020485,10020482,10048999,10020484,10020479,10020485,10020482,10048999,10020487,10020479,10020485,10020483,10020477,10020487,10020479,10020485,10020483,10020477,10020487,10020479,10020485,10020483,10020477,10020487,10020479,10020485,10020486,10020478,10020487,10020479,10020485,10020486,10020478,10020488,10020479,10020485,10020486,10020478,10020488,10020479,10020485,10020488,10020479,10020485,10020488,10020479,10020485,10020488,10020479,10020485,10020479,10020485,10020479,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020480,10020480,10020480,10020480,10020480,10020480,10020480</t>
+          <t>10020479,10048998,10020481,10048998,10020484,10020479,10048998,10020481,10048998,10020484,10020479,10020476,10020481,10020476,10020484,10020479,10020476,10020481,10020476,10020484,10020479,10020476,10020482,10020476,10020484,10020479,10048999,10020482,10048999,10020484,10020479,10048999,10020482,10048999,10020487,10020479,10020477,10020483,10020477,10020487,10020479,10020477,10020483,10020477,10020487,10020479,10020477,10020483,10020477,10020487,10020479,10020478,10020486,10020478,10020487,10020479,10020478,10020486,10020478,10020488,10020479,10020478,10020486,10020478,10020488,10020479,10020485,10020488,10020479,10020485,10020488,10020479,10020485,10020488,10020479,10020485,10020479,10020485,10020479,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020485,10020480,10020480,10020480,10020480,10020480,10020480,10020480,10020480</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L26 W10/25; N=110; EHP=4202.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x19,normal:18x19,fast:30x4,fast:58x3,fast:64x3,medium:83x6,swarm:84x30,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L26 W10/25; N=110; EHP=11638.221296; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,medium:83x6,medium:108x5,medium:123x5,normal:17x19,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10020489,10020498,10020491,10049000,10020497,10045283,10020489,10020498,10020491,10049000,10020497,10045284,10020489,10020498,10020491,10049000,10020497,10020494,10020489,10020498,10020492,10049001,10020497,10020494,10020489,10020498,10020492,10049001,10020497,10020495,10020489,10020498,10020492,10049001,10020502,10020495,10020489,10020498,10020493,10049002,10020502,10020496,10020489,10020498,10020493,10049002,10020502,10020499,10020489,10020498,10020493,10049002,10020502,10020500,10020489,10020498,10020501,10049003,10020502,10020504,10020489,10020498,10020501,10049003,10020502,10020504,10020489,10020498,10020501,10049004,10020503,10020489,10020498,10020501,10049004,10020503,10020489,10020498,10049004,10020503,10020489,10020498,10020503,10020490,10020498,10020503,10020490,10020498,10020503,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020498,10020498,10020498</t>
+          <t>10020489,10049000,10020491,10049000,10020497,10045283,10020489,10049000,10020491,10049000,10020497,10045284,10020489,10049000,10020491,10049000,10020497,10020494,10020489,10049001,10020492,10049001,10020497,10020494,10020489,10049001,10020492,10049001,10020497,10020495,10020489,10049001,10020492,10049001,10020502,10020495,10020489,10049002,10020493,10049002,10020502,10020496,10020489,10049002,10020493,10049002,10020502,10020499,10020489,10049002,10020493,10049002,10020502,10020500,10020489,10049003,10020501,10049003,10020502,10020504,10020489,10049003,10020501,10049003,10020502,10020504,10020489,10049004,10020501,10049004,10020503,10020489,10049004,10020501,10049004,10020503,10020489,10049004,10049004,10020503,10020489,10020498,10020503,10020490,10020498,10020503,10020490,10020498,10020503,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020490,10020498,10020498,10020498,10020498</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L26 W11/25; N=116; EHP=4287.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x15,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x32,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L26 W11/25; N=116; EHP=11860.128861; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10020508,10020518,10020510,10049005,10020517,10020511,10020508,10020518,10020510,10049005,10020517,10045285,10020508,10020518,10020510,10049005,10020517,10020514,10020508,10020518,10020512,10020505,10020517,10020514,10020508,10020518,10020512,10020505,10020517,10020515,10020508,10020518,10020512,10020505,10020517,10020515,10020508,10020518,10020512,10049006,10020522,10020516,10020508,10020518,10020513,10049006,10020522,10020516,10020508,10020518,10020513,10049006,10020522,10020519,10020508,10020518,10020513,10020506,10020522,10020520,10020508,10020518,10020513,10020506,10020522,10020520,10020508,10020518,10020521,10020506,10020522,10045286,10020508,10020518,10020521,10020507,10020523,10020508,10020518,10020521,10020507,10020523,10020509,10020518,10020507,10020523,10020509,10020518,10020523,10020509,10020518,10020523,10020509,10020518,10020523,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020518,10020518,10020518,10020518,10020518</t>
+          <t>10020508,10049005,10020510,10049005,10020517,10020511,10020508,10049005,10020510,10049005,10020517,10045285,10020508,10049005,10020510,10049005,10020517,10020514,10020508,10020505,10020512,10020505,10020517,10020514,10020508,10020505,10020512,10020505,10020517,10020515,10020508,10020505,10020512,10020505,10020517,10020515,10020508,10049006,10020512,10049006,10020522,10020516,10020508,10049006,10020513,10049006,10020522,10020516,10020508,10049006,10020513,10049006,10020522,10020519,10020508,10020506,10020513,10020506,10020522,10020520,10020508,10020506,10020513,10020506,10020522,10020520,10020508,10020506,10020521,10020506,10020522,10045286,10020508,10020507,10020521,10020507,10020523,10020508,10020507,10020521,10020507,10020523,10020509,10020507,10020507,10020523,10020509,10020518,10020523,10020509,10020518,10020523,10020509,10020518,10020523,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020509,10020518,10020518,10020518,10020518,10020518,10020518</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L26 W12/25; N=122; EHP=4435.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L26 W12/25; N=122; EHP=12271.903341; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10020527,10020537,10020529,10049007,10020536,10020530,10020527,10020537,10020529,10049007,10020536,10020531,10020527,10020537,10020529,10049007,10020536,10020534,10020527,10020537,10020529,10020524,10020536,10020534,10020527,10020537,10020532,10020524,10020536,10045287,10020527,10020537,10020532,10020524,10020536,10020535,10020527,10020537,10020532,10049008,10020536,10020535,10020527,10020537,10020533,10049008,10020541,10020538,10020527,10020537,10020533,10049008,10020541,10020538,10020527,10020537,10020533,10020525,10020541,10020539,10020527,10020537,10020533,10020525,10020541,10020539,10020527,10020537,10020540,10020525,10020541,10045288,10020527,10020537,10020540,10020526,10020541,10020527,10020537,10020540,10020526,10020542,10020527,10020537,10020540,10020526,10020542,10020527,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020537,10020537,10020537</t>
+          <t>10020527,10049007,10020529,10049007,10020536,10020530,10020527,10049007,10020529,10049007,10020536,10020531,10020527,10049007,10020529,10049007,10020536,10020534,10020527,10020524,10020529,10020524,10020536,10020534,10020527,10020524,10020532,10020524,10020536,10045287,10020527,10020524,10020532,10020524,10020536,10020535,10020527,10049008,10020532,10049008,10020536,10020535,10020527,10049008,10020533,10049008,10020541,10020538,10020527,10049008,10020533,10049008,10020541,10020538,10020527,10020525,10020533,10020525,10020541,10020539,10020527,10020525,10020533,10020525,10020541,10020539,10020527,10020525,10020540,10020525,10020541,10045288,10020527,10020526,10020540,10020526,10020541,10020527,10020526,10020540,10020526,10020542,10020527,10020526,10020540,10020526,10020542,10020527,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020542,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020528,10020537,10020537,10020537,10020537</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L26 W13/25; N=128; EHP=5409.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x35,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L26 W13/25; N=128; EHP=14958.854650; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10020546,10020555,10020548,10049009,10020554,10020549,10020546,10020555,10020548,10049009,10020554,10020549,10020546,10020555,10020548,10049009,10020554,10020550,10020546,10020555,10020548,10049009,10020554,10020550,10020546,10020555,10020551,10020543,10020554,10045289,10020546,10020555,10020551,10020543,10020554,10045290,10020546,10020555,10020551,10020543,10020559,10020553,10020546,10020555,10020551,10049010,10020559,10020553,10020546,10020555,10020552,10049010,10020559,10020556,10020546,10020555,10020552,10049010,10020559,10020556,10020546,10020555,10020552,10020544,10020559,10020557,10020546,10020555,10020552,10020544,10020559,10020557,10020546,10020555,10020558,10020544,10020559,10020561,10020546,10020555,10020558,10020545,10020560,10020546,10020555,10020558,10020545,10020560,10020546,10020555,10020558,10020545,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020555,10020555,10020555,10020555,10020555</t>
+          <t>10020546,10049009,10020548,10049009,10020554,10020549,10020546,10049009,10020548,10049009,10020554,10020549,10020546,10049009,10020548,10049009,10020554,10020550,10020546,10049009,10020548,10049009,10020554,10020550,10020546,10020543,10020551,10020543,10020554,10045289,10020546,10020543,10020551,10020543,10020554,10045290,10020546,10020543,10020551,10020543,10020559,10020553,10020546,10049010,10020551,10049010,10020559,10020553,10020546,10049010,10020552,10049010,10020559,10020556,10020546,10049010,10020552,10049010,10020559,10020556,10020546,10020544,10020552,10020544,10020559,10020557,10020546,10020544,10020552,10020544,10020559,10020557,10020546,10020544,10020558,10020544,10020559,10020561,10020546,10020545,10020558,10020545,10020560,10020546,10020545,10020558,10020545,10020560,10020546,10020545,10020558,10020545,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020560,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020547,10020555,10020555,10020555,10020555,10020555,10020555</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L26 W14/25; N=134; EHP=6524.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x37,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L26 W14/25; N=134; EHP=18045.853204; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10020565,10020577,10020567,10049011,10020576,10020568,10020572,10020565,10020577,10020567,10049011,10020576,10020568,10020565,10020577,10020567,10049011,10020576,10020569,10020565,10020577,10020567,10020562,10020576,10020569,10020565,10020577,10020570,10020562,10020576,10020573,10020565,10020577,10020570,10020562,10020576,10020574,10020565,10020577,10020570,10020562,10020576,10020574,10020565,10020577,10020570,10049012,10020580,10020575,10020565,10020577,10020571,10049012,10020580,10020575,10020565,10020577,10020571,10049012,10020580,10020578,10020565,10020577,10020571,10020563,10020580,10020578,10020565,10020577,10020571,10020563,10020580,10045291,10020565,10020577,10020579,10020563,10020580,10020582,10020565,10020577,10020579,10020563,10020580,10020582,10020565,10020577,10020579,10020564,10020581,10020565,10020577,10020579,10020564,10020581,10020566,10020577,10020564,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020577,10020577,10020577,10020577,10020577,10020577,10020577</t>
+          <t>10020565,10049011,10020567,10049011,10020576,10020568,10020572,10020565,10049011,10020567,10049011,10020576,10020568,10020565,10049011,10020567,10049011,10020576,10020569,10020565,10020562,10020567,10020562,10020576,10020569,10020565,10020562,10020570,10020562,10020576,10020573,10020565,10020562,10020570,10020562,10020576,10020574,10020565,10020562,10020570,10020562,10020576,10020574,10020565,10049012,10020570,10049012,10020580,10020575,10020565,10049012,10020571,10049012,10020580,10020575,10020565,10049012,10020571,10049012,10020580,10020578,10020565,10020563,10020571,10020563,10020580,10020578,10020565,10020563,10020571,10020563,10020580,10045291,10020565,10020563,10020579,10020563,10020580,10020582,10020565,10020563,10020579,10020563,10020580,10020582,10020565,10020564,10020579,10020564,10020581,10020565,10020564,10020579,10020564,10020581,10020566,10020564,10020564,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020581,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020566,10020577,10020577,10020577,10020577,10020577,10020577,10020577,10020577</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L26 W15/25; N=140; EHP=11386.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L26 W15/25; N=140; EHP=31490.361330; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x16,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10020583,10020593,10020585,10049013,10020592,10020586,10020583,10020593,10020585,10049013,10020592,10020586,10020583,10020593,10020585,10049013,10020592,10020587,10020583,10020593,10020585,10049014,10020592,10020587,10020583,10020593,10020588,10049014,10020592,10020590,10020583,10020593,10020588,10049014,10020592,10020590,10020583,10020593,10020588,10049014,10020592,10020591,10020583,10020593,10020588,10049015,10020597,10020591,10020583,10020593,10020588,10049015,10020597,10045292,10020583,10020593,10020589,10049015,10020597,10020594,10020583,10020593,10020589,10049015,10020597,10020594,10020583,10020593,10020589,10049016,10020597,10020595,10020583,10020593,10020589,10049016,10020597,10020599,10020583,10020593,10020596,10049016,10020597,10020599,10020583,10020593,10020596,10049017,10020598,10020583,10020593,10020596,10049017,10020598,10020583,10020593,10020596,10049017,10020598,10020583,10020593,10049017,10020598,10020584,10020593,10020598,10020584,10020593,10020598,10020584,10020593,10020598,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020593,10020593,10020593,10020593</t>
+          <t>10020583,10049013,10020585,10049013,10020592,10020586,10020583,10049013,10020585,10049013,10020592,10020586,10020583,10049013,10020585,10049013,10020592,10020587,10020583,10049014,10020585,10049014,10020592,10020587,10020583,10049014,10020588,10049014,10020592,10020590,10020583,10049014,10020588,10049014,10020592,10020590,10020583,10049014,10020588,10049014,10020592,10020591,10020583,10049015,10020588,10049015,10020597,10020591,10020583,10049015,10020588,10049015,10020597,10045292,10020583,10049015,10020589,10049015,10020597,10020594,10020583,10049015,10020589,10049015,10020597,10020594,10020583,10049016,10020589,10049016,10020597,10020595,10020583,10049016,10020589,10049016,10020597,10020599,10020583,10049016,10020596,10049016,10020597,10020599,10020583,10049017,10020596,10049017,10020598,10020583,10049017,10020596,10049017,10020598,10020583,10049017,10020596,10049017,10020598,10020583,10049017,10049017,10020598,10020584,10020593,10020598,10020584,10020593,10020598,10020584,10020593,10020598,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020584,10020593,10020593,10020593,10020593,10020593</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L26 W16/25; N=146; EHP=11614.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L26 W16/25; N=146; EHP=32139.227299; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10020603,10020614,10020605,10049018,10020613,10020606,10020603,10020614,10020605,10049018,10020613,10020606,10020603,10020614,10020605,10049018,10020613,10020607,10020603,10020614,10020605,10049018,10020613,10020607,10020603,10020614,10020605,10020600,10020613,10020610,10020603,10020614,10020608,10020600,10020613,10020610,10020603,10020614,10020608,10020600,10020613,10020611,10020603,10020614,10020608,10049019,10020617,10020611,10020603,10020614,10020608,10049019,10020617,10020612,10020603,10020614,10020609,10049019,10020617,10020612,10020603,10020614,10020609,10049019,10020617,10045293,10020603,10020614,10020609,10020601,10020617,10020615,10020603,10020614,10020609,10020601,10020617,10020615,10020603,10020614,10020609,10020601,10020617,10020619,10020603,10020614,10020616,10020602,10020618,10020619,10020603,10020614,10020616,10020602,10020618,10020603,10020614,10020616,10020602,10020618,10020603,10020614,10020616,10020602,10020618,10020603,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020614,10020614,10020614,10020614,10020614</t>
+          <t>10020603,10049018,10020605,10049018,10020613,10020606,10020603,10049018,10020605,10049018,10020613,10020606,10020603,10049018,10020605,10049018,10020613,10020607,10020603,10049018,10020605,10049018,10020613,10020607,10020603,10020600,10020605,10020600,10020613,10020610,10020603,10020600,10020608,10020600,10020613,10020610,10020603,10020600,10020608,10020600,10020613,10020611,10020603,10049019,10020608,10049019,10020617,10020611,10020603,10049019,10020608,10049019,10020617,10020612,10020603,10049019,10020609,10049019,10020617,10020612,10020603,10049019,10020609,10049019,10020617,10045293,10020603,10020601,10020609,10020601,10020617,10020615,10020603,10020601,10020609,10020601,10020617,10020615,10020603,10020601,10020609,10020601,10020617,10020619,10020603,10020602,10020616,10020602,10020618,10020619,10020603,10020602,10020616,10020602,10020618,10020603,10020602,10020616,10020602,10020618,10020603,10020602,10020616,10020602,10020618,10020603,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020618,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020604,10020614,10020614,10020614,10020614,10020614,10020614</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L26 W17/25; N=152; EHP=11847.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L26 W17/25; N=152; EHP=32766.788525; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10020623,10020633,10020625,10049020,10020632,10045294,10020623,10020633,10020625,10049020,10020632,10020626,10020623,10020633,10020625,10049020,10020632,10020626,10020623,10020633,10020625,10049020,10020632,10020629,10020623,10020633,10020625,10020620,10020632,10020629,10020623,10020633,10020627,10020620,10020632,10020630,10020623,10020633,10020627,10020620,10020632,10020630,10020623,10020633,10020627,10020620,10020632,10020631,10020623,10020633,10020627,10049021,10020637,10020631,10020623,10020633,10020628,10049021,10020637,10020634,10020623,10020633,10020628,10049021,10020637,10020634,10020623,10020633,10020628,10049021,10020637,10020635,10020623,10020633,10020628,10020621,10020637,10020635,10020623,10020633,10020636,10020621,10020637,10020639,10020623,10020633,10020636,10020621,10020637,10020639,10020623,10020633,10020636,10020621,10020637,10020623,10020633,10020636,10020622,10020638,10020623,10020633,10020636,10020622,10020638,10020623,10020633,10020622,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020633,10020633,10020633,10020633,10020633</t>
+          <t>10020623,10049020,10020625,10049020,10020632,10045294,10020623,10049020,10020625,10049020,10020632,10020626,10020623,10049020,10020625,10049020,10020632,10020626,10020623,10049020,10020625,10049020,10020632,10020629,10020623,10020620,10020625,10020620,10020632,10020629,10020623,10020620,10020627,10020620,10020632,10020630,10020623,10020620,10020627,10020620,10020632,10020630,10020623,10020620,10020627,10020620,10020632,10020631,10020623,10049021,10020627,10049021,10020637,10020631,10020623,10049021,10020628,10049021,10020637,10020634,10020623,10049021,10020628,10049021,10020637,10020634,10020623,10049021,10020628,10049021,10020637,10020635,10020623,10020621,10020628,10020621,10020637,10020635,10020623,10020621,10020636,10020621,10020637,10020639,10020623,10020621,10020636,10020621,10020637,10020639,10020623,10020621,10020636,10020621,10020637,10020623,10020622,10020636,10020622,10020638,10020623,10020622,10020636,10020622,10020638,10020623,10020622,10020622,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020638,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020624,10020633,10020633,10020633,10020633,10020633,10020633</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L26 W18/25; N=158; EHP=12656.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x20,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L26 W18/25; N=158; EHP=35012.376115; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10020643,10020653,10020645,10049022,10020652,10020646,10020643,10020653,10020645,10049022,10020652,10020646,10020643,10020653,10020645,10049022,10020652,10045295,10020643,10020653,10020645,10049022,10020652,10045295,10020643,10020653,10020647,10020640,10020652,10020649,10020643,10020653,10020647,10020640,10020652,10020649,10020643,10020653,10020647,10020640,10020652,10020650,10020643,10020653,10020647,10020640,10020652,10020650,10020643,10020653,10020647,10049023,10020657,10020651,10020643,10020653,10020648,10049023,10020657,10020651,10020643,10020653,10020648,10049023,10020657,10020654,10020643,10020653,10020648,10049023,10020657,10020654,10020643,10020653,10020648,10020641,10020657,10020655,10020643,10020653,10020648,10020641,10020657,10020655,10020643,10020653,10020656,10020641,10020657,10020659,10020643,10020653,10020656,10020641,10020657,10020659,10020643,10020653,10020656,10020642,10020658,10020643,10020653,10020656,10020642,10020658,10020643,10020653,10020656,10020642,10020658,10020643,10020653,10020642,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020653,10020653,10020653,10020653,10020653</t>
+          <t>10020643,10049022,10020645,10049022,10020652,10020646,10020643,10049022,10020645,10049022,10020652,10020646,10020643,10049022,10020645,10049022,10020652,10045295,10020643,10049022,10020645,10049022,10020652,10045295,10020643,10020640,10020647,10020640,10020652,10020649,10020643,10020640,10020647,10020640,10020652,10020649,10020643,10020640,10020647,10020640,10020652,10020650,10020643,10020640,10020647,10020640,10020652,10020650,10020643,10049023,10020647,10049023,10020657,10020651,10020643,10049023,10020648,10049023,10020657,10020651,10020643,10049023,10020648,10049023,10020657,10020654,10020643,10049023,10020648,10049023,10020657,10020654,10020643,10020641,10020648,10020641,10020657,10020655,10020643,10020641,10020648,10020641,10020657,10020655,10020643,10020641,10020656,10020641,10020657,10020659,10020643,10020641,10020656,10020641,10020657,10020659,10020643,10020642,10020656,10020642,10020658,10020643,10020642,10020656,10020642,10020658,10020643,10020642,10020656,10020642,10020658,10020643,10020642,10020642,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020658,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020644,10020653,10020653,10020653,10020653,10020653,10020653</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L26 W19/25; N=164; EHP=14659.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L26 W19/25; N=164; EHP=40558.409135; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10020663,10020675,10020665,10049024,10020674,10020666,10020670,10020663,10020675,10020665,10049024,10020674,10020666,10020663,10020675,10020665,10049024,10020674,10020667,10020663,10020675,10020665,10049024,10020674,10020667,10020663,10020675,10020665,10020660,10020674,10020671,10020663,10020675,10020668,10020660,10020674,10020671,10020663,10020675,10020668,10020660,10020674,10020672,10020663,10020675,10020668,10020660,10020674,10020672,10020663,10020675,10020668,10049025,10020679,10020672,10020663,10020675,10020668,10049025,10020679,10020673,10020663,10020675,10020669,10049025,10020679,10020673,10020663,10020675,10020669,10049025,10020679,10020676,10020663,10020675,10020669,10020661,10020679,10020676,10020663,10020675,10020669,10020661,10020679,10020677,10020663,10020675,10020669,10020661,10020679,10020677,10020663,10020675,10020678,10020661,10020679,10020681,10020663,10020675,10020678,10020662,10020680,10020681,10020663,10020675,10020678,10020662,10020680,10020663,10020675,10020678,10020662,10020680,10020663,10020675,10020678,10020662,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020675,10020675,10020675,10020675,10020675,10020675,10020675</t>
+          <t>10020663,10049024,10020665,10049024,10020674,10020666,10020670,10020663,10049024,10020665,10049024,10020674,10020666,10020663,10049024,10020665,10049024,10020674,10020667,10020663,10049024,10020665,10049024,10020674,10020667,10020663,10020660,10020665,10020660,10020674,10020671,10020663,10020660,10020668,10020660,10020674,10020671,10020663,10020660,10020668,10020660,10020674,10020672,10020663,10020660,10020668,10020660,10020674,10020672,10020663,10049025,10020668,10049025,10020679,10020672,10020663,10049025,10020668,10049025,10020679,10020673,10020663,10049025,10020669,10049025,10020679,10020673,10020663,10049025,10020669,10049025,10020679,10020676,10020663,10020661,10020669,10020661,10020679,10020676,10020663,10020661,10020669,10020661,10020679,10020677,10020663,10020661,10020669,10020661,10020679,10020677,10020663,10020661,10020678,10020661,10020679,10020681,10020663,10020662,10020678,10020662,10020680,10020681,10020663,10020662,10020678,10020662,10020680,10020663,10020662,10020678,10020662,10020680,10020663,10020662,10020678,10020662,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020680,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020664,10020675,10020675,10020675,10020675,10020675,10020675,10020675,10020675</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L26 W20/25; N=170; EHP=24604.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L26 W20/25; N=170; EHP=68026.884629; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10020685,10020696,10020687,10049026,10020695,10020688,10020685,10020696,10020687,10049026,10020695,10020688,10020685,10020696,10020687,10049026,10020695,10020689,10020685,10020696,10020687,10049026,10020695,10020689,10020685,10020696,10020687,10020682,10020695,10020692,10020685,10020696,10020690,10020682,10020695,10020692,10020685,10020696,10020690,10020682,10020695,10020692,10020685,10020696,10020690,10020682,10020695,10020693,10020685,10020696,10020690,10020682,10020695,10020693,10020685,10020696,10020690,10049027,10020700,10020694,10020685,10020696,10020691,10049027,10020700,10020694,10020685,10020696,10020691,10049027,10020700,10020697,10020685,10020696,10020691,10049027,10020700,10020697,10020685,10020696,10020691,10020683,10020700,10020698,10020685,10020696,10020691,10020683,10020700,10020698,10020685,10020696,10020691,10020683,10020700,10020702,10020685,10020696,10020699,10020683,10020700,10020702,10020685,10020696,10020699,10020684,10020700,10020685,10020696,10020699,10020684,10020701,10020685,10020696,10020699,10020684,10020701,10020685,10020696,10020699,10020684,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020696,10020696,10020696,10020696,10020696,10020696,10020696</t>
+          <t>10020685,10049026,10020687,10049026,10020695,10020688,10020685,10049026,10020687,10049026,10020695,10020688,10020685,10049026,10020687,10049026,10020695,10020689,10020685,10049026,10020687,10049026,10020695,10020689,10020685,10020682,10020687,10020682,10020695,10020692,10020685,10020682,10020690,10020682,10020695,10020692,10020685,10020682,10020690,10020682,10020695,10020692,10020685,10020682,10020690,10020682,10020695,10020693,10020685,10020682,10020690,10020682,10020695,10020693,10020685,10049027,10020690,10049027,10020700,10020694,10020685,10049027,10020691,10049027,10020700,10020694,10020685,10049027,10020691,10049027,10020700,10020697,10020685,10049027,10020691,10049027,10020700,10020697,10020685,10020683,10020691,10020683,10020700,10020698,10020685,10020683,10020691,10020683,10020700,10020698,10020685,10020683,10020691,10020683,10020700,10020702,10020685,10020683,10020699,10020683,10020700,10020702,10020685,10020684,10020699,10020684,10020700,10020685,10020684,10020699,10020684,10020701,10020685,10020684,10020699,10020684,10020701,10020685,10020684,10020699,10020684,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020701,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020686,10020696,10020696,10020696,10020696,10020696,10020696,10020696,10020696</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L26 W21/25; N=176; EHP=25097.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L26 W21/25; N=176; EHP=69421.305404; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10020706,10020717,10020708,10049028,10020716,10020709,10020706,10020717,10020708,10049028,10020716,10020709,10020706,10020717,10020708,10049028,10020716,10020710,10020706,10020717,10020708,10049028,10020716,10020710,10020706,10020717,10020708,10020703,10020716,10020713,10020706,10020717,10020708,10020703,10020716,10020713,10020706,10020717,10020711,10020703,10020716,10020714,10020706,10020717,10020711,10020703,10020716,10020714,10020706,10020717,10020711,10049029,10020716,10020715,10020706,10020717,10020711,10049029,10020721,10020715,10020706,10020717,10020711,10049029,10020721,10020715,10020706,10020717,10020712,10049029,10020721,10020718,10020706,10020717,10020712,10049029,10020721,10020718,10020706,10020717,10020712,10020704,10020721,10020719,10020706,10020717,10020712,10020704,10020721,10020719,10020706,10020717,10020712,10020704,10020721,10020719,10020706,10020717,10020720,10020704,10020721,10020723,10020706,10020717,10020720,10020705,10020721,10020723,10020706,10020717,10020720,10020705,10020722,10020706,10020717,10020720,10020705,10020722,10020706,10020717,10020720,10020705,10020722,10020706,10020717,10020705,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020717,10020717,10020717,10020717,10020717,10020717</t>
+          <t>10020706,10049028,10020708,10049028,10020716,10020709,10020706,10049028,10020708,10049028,10020716,10020709,10020706,10049028,10020708,10049028,10020716,10020710,10020706,10049028,10020708,10049028,10020716,10020710,10020706,10020703,10020708,10020703,10020716,10020713,10020706,10020703,10020708,10020703,10020716,10020713,10020706,10020703,10020711,10020703,10020716,10020714,10020706,10020703,10020711,10020703,10020716,10020714,10020706,10049029,10020711,10049029,10020716,10020715,10020706,10049029,10020711,10049029,10020721,10020715,10020706,10049029,10020711,10049029,10020721,10020715,10020706,10049029,10020712,10049029,10020721,10020718,10020706,10049029,10020712,10049029,10020721,10020718,10020706,10020704,10020712,10020704,10020721,10020719,10020706,10020704,10020712,10020704,10020721,10020719,10020706,10020704,10020712,10020704,10020721,10020719,10020706,10020704,10020720,10020704,10020721,10020723,10020706,10020705,10020720,10020705,10020721,10020723,10020706,10020705,10020720,10020705,10020722,10020706,10020705,10020720,10020705,10020722,10020706,10020705,10020720,10020705,10020722,10020706,10020705,10020705,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020722,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020707,10020717,10020717,10020717,10020717,10020717,10020717,10020717</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L26 W22/25; N=182; EHP=25599.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L26 W22/25; N=182; EHP=70817.114680; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10020727,10020738,10020729,10049030,10020737,10020730,10020727,10020738,10020729,10049030,10020737,10020730,10020727,10020738,10020729,10049030,10020737,10020731,10020727,10020738,10020729,10049030,10020737,10020731,10020727,10020738,10020729,10049030,10020737,10020734,10020727,10020738,10020732,10020724,10020737,10020734,10020727,10020738,10020732,10020724,10020737,10020735,10020727,10020738,10020732,10020724,10020737,10020735,10020727,10020738,10020732,10020724,10020737,10020736,10020727,10020738,10020732,10049031,10020742,10020736,10020727,10020738,10020732,10049031,10020742,10020736,10020727,10020738,10020733,10049031,10020742,10020739,10020727,10020738,10020733,10049031,10020742,10020739,10020727,10020738,10020733,10049031,10020742,10020739,10020727,10020738,10020733,10020725,10020742,10020740,10020727,10020738,10020733,10020725,10020742,10020740,10020727,10020738,10020741,10020725,10020742,10020744,10020727,10020738,10020741,10020725,10020742,10020744,10020727,10020738,10020741,10020725,10020743,10020727,10020738,10020741,10020726,10020743,10020727,10020738,10020741,10020726,10020743,10020727,10020738,10020741,10020726,10020743,10020727,10020738,10020726,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020738,10020738,10020738,10020738,10020738,10020738,10020738</t>
+          <t>10020727,10049030,10020729,10049030,10020737,10020730,10020727,10049030,10020729,10049030,10020737,10020730,10020727,10049030,10020729,10049030,10020737,10020731,10020727,10049030,10020729,10049030,10020737,10020731,10020727,10049030,10020729,10049030,10020737,10020734,10020727,10020724,10020732,10020724,10020737,10020734,10020727,10020724,10020732,10020724,10020737,10020735,10020727,10020724,10020732,10020724,10020737,10020735,10020727,10020724,10020732,10020724,10020737,10020736,10020727,10049031,10020732,10049031,10020742,10020736,10020727,10049031,10020732,10049031,10020742,10020736,10020727,10049031,10020733,10049031,10020742,10020739,10020727,10049031,10020733,10049031,10020742,10020739,10020727,10049031,10020733,10049031,10020742,10020739,10020727,10020725,10020733,10020725,10020742,10020740,10020727,10020725,10020733,10020725,10020742,10020740,10020727,10020725,10020741,10020725,10020742,10020744,10020727,10020725,10020741,10020725,10020742,10020744,10020727,10020725,10020741,10020725,10020743,10020727,10020726,10020741,10020726,10020743,10020727,10020726,10020741,10020726,10020743,10020727,10020726,10020741,10020726,10020743,10020727,10020726,10020726,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020743,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020728,10020738,10020738,10020738,10020738,10020738,10020738,10020738,10020738</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L26 W23/25; N=188; EHP=26111.000000; air:2x5,air:11x4,air:12x5,air:13x5,air:14x4,normal:17x23,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x52,heavy:86x3,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x2</t>
+          <t>L26 W23/25; N=188; EHP=72247.625290; air:2x10,air:11x8,air:12x10,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x10,normal:17x23,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10020748,10020759,10020750,10049032,10020758,10020751,10020748,10020759,10020750,10049032,10020758,10020751,10020748,10020759,10020750,10049032,10020758,10020751,10020748,10020759,10020750,10049032,10020758,10020752,10020748,10020759,10020750,10049032,10020758,10020752,10020748,10020759,10020750,10020745,10020758,10020752,10020748,10020759,10020753,10020745,10020758,10020755,10020748,10020759,10020753,10020745,10020758,10020755,10020748,10020759,10020753,10020745,10020758,10020756,10020748,10020759,10020753,10020745,10020758,10020756,10020748,10020759,10020753,10049033,10020763,10020757,10020748,10020759,10020753,10049033,10020763,10020757,10020748,10020759,10020754,10049033,10020763,10020760,10020748,10020759,10020754,10049033,10020763,10020760,10020748,10020759,10020754,10020746,10020763,10020760,10020748,10020759,10020754,10020746,10020763,10020761,10020748,10020759,10020754,10020746,10020763,10020761,10020748,10020759,10020754,10020746,10020763,10020765,10020748,10020759,10020762,10020746,10020763,10020765,10020748,10020759,10020762,10020747,10020763,10020748,10020759,10020762,10020747,10020764,10020748,10020759,10020762,10020747,10020764,10020748,10020759,10020762,10020747,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020759,10020759,10020759,10020759,10020759,10020759,10020759,10020759</t>
+          <t>10020748,10049032,10020750,10049032,10020758,10020751,10020748,10049032,10020750,10049032,10020758,10020751,10020748,10049032,10020750,10049032,10020758,10020751,10020748,10049032,10020750,10049032,10020758,10020752,10020748,10049032,10020750,10049032,10020758,10020752,10020748,10020745,10020750,10020745,10020758,10020752,10020748,10020745,10020753,10020745,10020758,10020755,10020748,10020745,10020753,10020745,10020758,10020755,10020748,10020745,10020753,10020745,10020758,10020756,10020748,10020745,10020753,10020745,10020758,10020756,10020748,10049033,10020753,10049033,10020763,10020757,10020748,10049033,10020753,10049033,10020763,10020757,10020748,10049033,10020754,10049033,10020763,10020760,10020748,10049033,10020754,10049033,10020763,10020760,10020748,10020746,10020754,10020746,10020763,10020760,10020748,10020746,10020754,10020746,10020763,10020761,10020748,10020746,10020754,10020746,10020763,10020761,10020748,10020746,10020754,10020746,10020763,10020765,10020748,10020746,10020762,10020746,10020763,10020765,10020748,10020747,10020762,10020747,10020763,10020748,10020747,10020762,10020747,10020764,10020748,10020747,10020762,10020747,10020764,10020748,10020747,10020762,10020747,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020764,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020749,10020759,10020759,10020759,10020759,10020759,10020759,10020759,10020759,10020759</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L26 W24/25; N=194; EHP=27961.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x6,heavy:31x3,heavy:40x3,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x54,heavy:86x3,heavy:88x2,fast:98x5,medium:108x10,medium:123x9,heavy:127x2</t>
+          <t>L26 W24/25; N=194; EHP=77335.014879; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x10,medium:108x10,medium:123x9,normal:17x23,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10020769,10020780,10020771,10049034,10020779,10020772,10020787,10020769,10020780,10020771,10049034,10020779,10020772,10020769,10020780,10020771,10049034,10020779,10020772,10020769,10020780,10020771,10049034,10020779,10020773,10020769,10020780,10020771,10020766,10020779,10020773,10020769,10020780,10020771,10020766,10020779,10020773,10020769,10020780,10020774,10020766,10020779,10020776,10020769,10020780,10020774,10020766,10020779,10020776,10020769,10020780,10020774,10020766,10020779,10020777,10020769,10020780,10020774,10049035,10020779,10020777,10020769,10020780,10020774,10049035,10020784,10020777,10020769,10020780,10020774,10049035,10020784,10020778,10020769,10020780,10020775,10049035,10020784,10020778,10020769,10020780,10020775,10049035,10020784,10020781,10020769,10020780,10020775,10020767,10020784,10020781,10020769,10020780,10020775,10020767,10020784,10020782,10020769,10020780,10020775,10020767,10020784,10020782,10020769,10020780,10020775,10020767,10020784,10020786,10020769,10020780,10020783,10020767,10020784,10020786,10020769,10020780,10020783,10020768,10020784,10020786,10020769,10020780,10020783,10020768,10020785,10020769,10020780,10020783,10020768,10020785,10020769,10020780,10020783,10020768,10020785,10020770,10020780,10020783,10020768,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780</t>
+          <t>10020769,10049034,10020771,10049034,10020779,10020772,10020787,10020769,10049034,10020771,10049034,10020779,10020772,10020769,10049034,10020771,10049034,10020779,10020772,10020769,10049034,10020771,10049034,10020779,10020773,10020769,10020766,10020771,10020766,10020779,10020773,10020769,10020766,10020771,10020766,10020779,10020773,10020769,10020766,10020774,10020766,10020779,10020776,10020769,10020766,10020774,10020766,10020779,10020776,10020769,10020766,10020774,10020766,10020779,10020777,10020769,10049035,10020774,10049035,10020779,10020777,10020769,10049035,10020774,10049035,10020784,10020777,10020769,10049035,10020774,10049035,10020784,10020778,10020769,10049035,10020775,10049035,10020784,10020778,10020769,10049035,10020775,10049035,10020784,10020781,10020769,10020767,10020775,10020767,10020784,10020781,10020769,10020767,10020775,10020767,10020784,10020782,10020769,10020767,10020775,10020767,10020784,10020782,10020769,10020767,10020775,10020767,10020784,10020786,10020769,10020767,10020783,10020767,10020784,10020786,10020769,10020768,10020783,10020768,10020784,10020786,10020769,10020768,10020783,10020768,10020785,10020769,10020768,10020783,10020768,10020785,10020769,10020768,10020783,10020768,10020785,10020770,10020768,10020783,10020768,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020785,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020770,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780,10020780</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L26 W25/25; N=200; EHP=55804.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x23,normal:18x22,fast:30x6,heavy:31x3,heavy:40x3,fast:58x6,fast:64x6,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x56,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x10,heavy:127x3,boss:132x1</t>
+          <t>L26 W25/25; N=200; EHP=154329.669359; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x6,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x10,medium:123x10,normal:17x23,normal:18x22,swarm:84x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L26/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L26/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>223</v>
+        <v>360</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>209</v>
+        <v>390</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>202</v>
+        <v>370</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>181</v>
+        <v>340</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>174</v>
+        <v>310</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>167</v>
+        <v>390</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>153</v>
+        <v>340</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>139</v>
+        <v>330</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>132</v>
+        <v>300</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
